--- a/docs/PRAP_UI_Component_List_v2.8.xlsx
+++ b/docs/PRAP_UI_Component_List_v2.8.xlsx
@@ -3232,7 +3232,7 @@
       <c r="G53" s="8" t="inlineStr"/>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>R-42; moved and the control given the count at R-52; narrowed by direction, project and smallest gap at R-53 — which narrows the LIST and never the count, since the count is the alarm.</t>
+          <t>R-42; moved and the control given the count at R-52; narrowed by direction, project and smallest gap at R-53 — which narrows the LIST and never the count, since the count is the alarm. Ordered by project ID, then month, ascending, every month listed (R-62 follow-up; was largest first, capped at 40).</t>
         </is>
       </c>
       <c r="I53" s="9" t="inlineStr"/>
